--- a/src/tokutei/shinsei/kitakyushu.xlsx
+++ b/src/tokutei/shinsei/kitakyushu.xlsx
@@ -1043,7 +1043,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1027430" y="156781"/>
-          <a:ext cx="730250" cy="left"/>
+          <a:ext cx="730250" cy="167640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1094,7 +1094,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5843270" y="3312150"/>
-          <a:ext cx="127000" cy="left"/>
+          <a:ext cx="127000" cy="127000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1145,7 +1145,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3387090" y="4150678"/>
-          <a:ext cx="146050" cy="left"/>
+          <a:ext cx="146050" cy="137160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1196,7 +1196,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="871220" y="4163251"/>
-          <a:ext cx="134163" cy="left"/>
+          <a:ext cx="134163" cy="137160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1247,7 +1247,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5615305" y="9173178"/>
-          <a:ext cx="165100" cy="left"/>
+          <a:ext cx="165100" cy="160020"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1303,7 +1303,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="425450" y="3347656"/>
-          <a:ext cx="5200650" cy="left"/>
+          <a:ext cx="5200650" cy="167641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1354,7 +1354,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="432575" y="3487356"/>
-          <a:ext cx="5719305" cy="left"/>
+          <a:ext cx="5719305" cy="167641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1405,7 +1405,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="565150" y="3627056"/>
-          <a:ext cx="3244850" cy="left"/>
+          <a:ext cx="3244850" cy="167641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1456,7 +1456,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="432575" y="3766756"/>
-          <a:ext cx="5718810" cy="left"/>
+          <a:ext cx="5718810" cy="167641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1512,7 +1512,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1265034" y="59380"/>
-          <a:ext cx="1511921" cy="left"/>
+          <a:ext cx="1511921" cy="198120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1563,7 +1563,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3466313" y="59380"/>
-          <a:ext cx="1518968" cy="left"/>
+          <a:ext cx="1518968" cy="198120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1614,7 +1614,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2746362" y="109913"/>
-          <a:ext cx="752079" cy="left"/>
+          <a:ext cx="752079" cy="121920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
